--- a/Donnees_TMs/Année 1/Liste sujets TM + jauge_année 1.xlsx
+++ b/Donnees_TMs/Année 1/Liste sujets TM + jauge_année 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bab1b6/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/pg52ygx_eduvaud_ch/Documents/Documents/TM/TM-code/Donnees_TMs/Année 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFA1289-9457-7344-A7A2-8A705FBE0BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{0BFA1289-9457-7344-A7A2-8A705FBE0BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D0D1E7A-5733-4180-A661-E509A8D3FB07}"/>
   <bookViews>
-    <workbookView xWindow="4260" yWindow="500" windowWidth="19860" windowHeight="13780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3690" yWindow="2295" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -579,16 +579,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="9" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="45.75" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -605,7 +605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="30" customHeight="1">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -620,7 +620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -635,7 +635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -650,7 +650,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="30" customHeight="1">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -667,7 +667,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -699,7 +699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -714,7 +714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -729,7 +729,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="30" customHeight="1">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -747,7 +747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="30" customHeight="1">
       <c r="A11" s="8">
         <v>10</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -779,7 +779,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="8">
         <v>12</v>
       </c>
@@ -794,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -809,7 +809,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="8">
         <v>14</v>
       </c>
@@ -824,7 +824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="8">
         <v>15</v>
       </c>
@@ -839,7 +839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="30" customHeight="1">
       <c r="A17" s="8">
         <v>16</v>
       </c>
@@ -856,7 +856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="30" customHeight="1">
       <c r="A18" s="8">
         <v>17</v>
       </c>
@@ -873,7 +873,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="30" customHeight="1">
       <c r="A19" s="8">
         <v>18</v>
       </c>
@@ -888,7 +888,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="30" customHeight="1">
       <c r="A20" s="8">
         <v>19</v>
       </c>
@@ -905,7 +905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="30" customHeight="1">
       <c r="A21" s="8">
         <v>20</v>
       </c>
@@ -920,7 +920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="8">
         <v>21</v>
       </c>
@@ -935,7 +935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="30" customHeight="1">
       <c r="A23" s="8">
         <v>22</v>
       </c>
@@ -950,7 +950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="30" customHeight="1">
       <c r="A24" s="8">
         <v>23</v>
       </c>
@@ -967,7 +967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="30" customHeight="1">
       <c r="A25" s="8">
         <v>24</v>
       </c>
@@ -982,7 +982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="30" customHeight="1">
       <c r="A26" s="8">
         <v>25</v>
       </c>
@@ -997,7 +997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="30" customHeight="1">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="30" customHeight="1">
       <c r="A28" s="10">
         <v>27</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="30" customHeight="1">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="30" customHeight="1">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="30" customHeight="1">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="31.5" customHeight="1">
       <c r="A32" s="8">
         <v>31</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="29.25" customHeight="1">
       <c r="A33" s="8">
         <v>32</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="29.25" customHeight="1">
       <c r="A34" s="8">
         <v>33</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="29.25" customHeight="1">
       <c r="A35" s="8">
         <v>34</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="25.5" customHeight="1">
       <c r="A36" s="8">
         <v>35</v>
       </c>
@@ -1147,11 +1147,8 @@
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E37" s="5">
-        <f>SUM(E2:E36)</f>
-        <v>238</v>
-      </c>
+    <row r="37" spans="1:5">
+      <c r="E37" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Donnees_TMs/Année 1/Liste sujets TM + jauge_année 1.xlsx
+++ b/Donnees_TMs/Année 1/Liste sujets TM + jauge_année 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/pg52ygx_eduvaud_ch/Documents/Documents/TM/TM-code/Donnees_TMs/Année 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{0BFA1289-9457-7344-A7A2-8A705FBE0BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D0D1E7A-5733-4180-A661-E509A8D3FB07}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{0BFA1289-9457-7344-A7A2-8A705FBE0BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5010AE4A-93CD-4B68-B137-8EA9A196D34D}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="2295" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -47,9 +47,6 @@
     <t>Individuel/groupe/ indifférent</t>
   </si>
   <si>
-    <t>Nombre minmal travaux</t>
-  </si>
-  <si>
     <t>Nombre maximal travaux</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>Angl/ Fr</t>
+  </si>
+  <si>
+    <t>Nombre minimal travaux</t>
   </si>
 </sst>
 </file>
@@ -599,10 +599,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
@@ -610,10 +610,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
@@ -625,10 +625,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2">
@@ -640,10 +640,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2">
@@ -655,10 +655,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
@@ -672,16 +672,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2">
         <v>8</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
@@ -689,10 +689,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2">
@@ -704,10 +704,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2">
@@ -719,10 +719,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2">
@@ -734,17 +734,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1">
@@ -752,10 +752,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -769,10 +769,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2">
@@ -784,14 +784,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
@@ -799,10 +799,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2">
@@ -814,10 +814,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2">
@@ -829,10 +829,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2">
@@ -844,10 +844,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="2">
         <v>8</v>
@@ -861,10 +861,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2">
         <v>6</v>
@@ -878,10 +878,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2">
@@ -893,10 +893,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="2">
         <v>4</v>
@@ -910,10 +910,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2">
@@ -925,10 +925,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2">
@@ -940,10 +940,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2">
@@ -955,10 +955,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" s="2">
         <v>3</v>
@@ -972,10 +972,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2">
@@ -987,10 +987,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2">
@@ -1002,10 +1002,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -1019,10 +1019,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="11">
@@ -1034,10 +1034,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2">
@@ -1049,10 +1049,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2">
@@ -1064,10 +1064,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2">
@@ -1079,10 +1079,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2">
@@ -1094,10 +1094,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2">
@@ -1109,10 +1109,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2">
@@ -1124,10 +1124,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2">
@@ -1139,10 +1139,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
